--- a/test/excel/keep/struct-open/all-insert-cols.xlsx
+++ b/test/excel/keep/struct-open/all-insert-cols.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-59473/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-77939/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{723CDACC-16B8-2F4E-B621-4EBEC3702011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A13511E2-9D1A-5445-A71C-A3C31596D3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId5"/>
+    <pivotCache cacheId="21" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
   <si>
     <t>Region</t>
   </si>
@@ -122,12 +122,39 @@
   <si>
     <t>plain</t>
   </si>
+  <si>
+    <r>
+      <t>Eas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>outh</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -139,8 +166,19 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -174,7 +212,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -695,7 +733,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1081,7 +1119,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -1118,7 +1156,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>35</v>
